--- a/quality attribute assessment sheet.xlsx
+++ b/quality attribute assessment sheet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phili\Dropbox\04_Research\04_QualiTact-Project-Analysis\01_Quality Attributes Categorization based on ISO and Mapping Study\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phili\Dropbox\01_Dev\02_QualiTact\Repository\QualiTact\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FFD1F0E-6885-4E93-811B-FB35B603807C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA84B9A-F86C-40EA-B186-5356D829BF9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="144" yWindow="2628" windowWidth="19296" windowHeight="8796" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Quality-Attribute-Assessment" sheetId="1" r:id="rId1"/>
@@ -396,9 +396,6 @@
     <t>Degree to which a system supports assessment by external tools to prove fulfillment of properties.</t>
   </si>
   <si>
-    <t>https://doi.org/10.5281/zenodo.8237328</t>
-  </si>
-  <si>
     <t xml:space="preserve">Degree to which a system, product or component is composed of parts that perform its functions and fulfill its responsibilities with fewer or more efficient use of resources </t>
   </si>
   <si>
@@ -427,6 +424,9 @@
   </si>
   <si>
     <t>Available in QualiTact Model?</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1145/3611643.3616242</t>
   </si>
 </sst>
 </file>
@@ -485,10 +485,10 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -798,7 +798,7 @@
         <v>103</v>
       </c>
       <c r="F1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -813,8 +813,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="4"/>
+      <c r="A3" s="4"/>
+      <c r="B3" s="5"/>
       <c r="C3" t="s">
         <v>3</v>
       </c>
@@ -826,8 +826,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="5"/>
-      <c r="B4" s="4"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="5"/>
       <c r="C4" t="s">
         <v>4</v>
       </c>
@@ -839,8 +839,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="4"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="5"/>
       <c r="C5" t="s">
         <v>5</v>
       </c>
@@ -852,8 +852,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="4"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
       <c r="C6" t="s">
         <v>6</v>
       </c>
@@ -883,8 +883,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="4"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
       <c r="C8" t="s">
         <v>8</v>
       </c>
@@ -899,8 +899,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="5"/>
-      <c r="B9" s="4"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="5"/>
       <c r="C9" t="s">
         <v>9</v>
       </c>
@@ -915,8 +915,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="4"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
       <c r="C10" t="s">
         <v>10</v>
       </c>
@@ -943,8 +943,8 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="4"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="5"/>
       <c r="C12" t="s">
         <v>12</v>
       </c>
@@ -956,8 +956,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="5"/>
-      <c r="B13" s="4"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="5"/>
       <c r="C13" t="s">
         <v>13</v>
       </c>
@@ -987,8 +987,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="4"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
       <c r="C15" t="s">
         <v>15</v>
       </c>
@@ -1000,8 +1000,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="5"/>
-      <c r="B16" s="4"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
       <c r="C16" t="s">
         <v>16</v>
       </c>
@@ -1013,8 +1013,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="4"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
       <c r="C17" t="s">
         <v>17</v>
       </c>
@@ -1026,8 +1026,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="4"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
       <c r="C18" t="s">
         <v>18</v>
       </c>
@@ -1039,8 +1039,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="4"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
       <c r="C19" t="s">
         <v>19</v>
       </c>
@@ -1052,8 +1052,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="4"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="5"/>
       <c r="C20" t="s">
         <v>20</v>
       </c>
@@ -1065,8 +1065,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="4"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
       <c r="C21" t="s">
         <v>21</v>
       </c>
@@ -1078,8 +1078,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="5"/>
-      <c r="B22" s="4"/>
+      <c r="A22" s="4"/>
+      <c r="B22" s="5"/>
       <c r="C22" t="s">
         <v>101</v>
       </c>
@@ -1103,8 +1103,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="4"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="5"/>
       <c r="C24" t="s">
         <v>23</v>
       </c>
@@ -1116,8 +1116,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="4"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="5"/>
       <c r="C25" t="s">
         <v>24</v>
       </c>
@@ -1129,8 +1129,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="4"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="5"/>
       <c r="C26" t="s">
         <v>25</v>
       </c>
@@ -1145,8 +1145,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
-      <c r="B27" s="4"/>
+      <c r="A27" s="4"/>
+      <c r="B27" s="5"/>
       <c r="C27" t="s">
         <v>26</v>
       </c>
@@ -1158,8 +1158,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="4"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="5"/>
       <c r="C28" t="s">
         <v>27</v>
       </c>
@@ -1186,8 +1186,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-      <c r="B30" s="4"/>
+      <c r="A30" s="4"/>
+      <c r="B30" s="5"/>
       <c r="C30" t="s">
         <v>29</v>
       </c>
@@ -1202,8 +1202,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
-      <c r="B31" s="4"/>
+      <c r="A31" s="4"/>
+      <c r="B31" s="5"/>
       <c r="C31" t="s">
         <v>30</v>
       </c>
@@ -1215,8 +1215,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="5"/>
-      <c r="B32" s="4"/>
+      <c r="A32" s="4"/>
+      <c r="B32" s="5"/>
       <c r="C32" t="s">
         <v>31</v>
       </c>
@@ -1228,8 +1228,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="5"/>
-      <c r="B33" s="4"/>
+      <c r="A33" s="4"/>
+      <c r="B33" s="5"/>
       <c r="C33" t="s">
         <v>32</v>
       </c>
@@ -1241,8 +1241,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="5"/>
-      <c r="B34" s="4"/>
+      <c r="A34" s="4"/>
+      <c r="B34" s="5"/>
       <c r="C34" t="s">
         <v>33</v>
       </c>
@@ -1254,8 +1254,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
-      <c r="B35" s="4"/>
+      <c r="A35" s="4"/>
+      <c r="B35" s="5"/>
       <c r="C35" t="s">
         <v>34</v>
       </c>
@@ -1279,8 +1279,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="5"/>
-      <c r="B37" s="4"/>
+      <c r="A37" s="4"/>
+      <c r="B37" s="5"/>
       <c r="C37" t="s">
         <v>36</v>
       </c>
@@ -1295,8 +1295,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="5"/>
-      <c r="B38" s="4"/>
+      <c r="A38" s="4"/>
+      <c r="B38" s="5"/>
       <c r="C38" t="s">
         <v>37</v>
       </c>
@@ -1308,8 +1308,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="5"/>
-      <c r="B39" s="4"/>
+      <c r="A39" s="4"/>
+      <c r="B39" s="5"/>
       <c r="C39" t="s">
         <v>38</v>
       </c>
@@ -1321,8 +1321,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="5"/>
-      <c r="B40" s="4"/>
+      <c r="A40" s="4"/>
+      <c r="B40" s="5"/>
       <c r="C40" t="s">
         <v>39</v>
       </c>
@@ -1337,8 +1337,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="5"/>
-      <c r="B41" s="4"/>
+      <c r="A41" s="4"/>
+      <c r="B41" s="5"/>
       <c r="C41" t="s">
         <v>40</v>
       </c>
@@ -1365,8 +1365,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="5"/>
-      <c r="B43" s="4"/>
+      <c r="A43" s="4"/>
+      <c r="B43" s="5"/>
       <c r="C43" t="s">
         <v>42</v>
       </c>
@@ -1378,8 +1378,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="5"/>
-      <c r="B44" s="4"/>
+      <c r="A44" s="4"/>
+      <c r="B44" s="5"/>
       <c r="C44" t="s">
         <v>43</v>
       </c>
@@ -1391,8 +1391,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="5"/>
-      <c r="B45" s="4"/>
+      <c r="A45" s="4"/>
+      <c r="B45" s="5"/>
       <c r="C45" t="s">
         <v>44</v>
       </c>
@@ -1404,10 +1404,10 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="5" t="s">
         <v>110</v>
       </c>
       <c r="C46" t="s">
@@ -1421,8 +1421,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="5"/>
-      <c r="B47" s="4"/>
+      <c r="A47" s="4"/>
+      <c r="B47" s="5"/>
       <c r="C47" t="s">
         <v>46</v>
       </c>
@@ -1437,8 +1437,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="5"/>
-      <c r="B48" s="4"/>
+      <c r="A48" s="4"/>
+      <c r="B48" s="5"/>
       <c r="C48" t="s">
         <v>96</v>
       </c>
@@ -1450,8 +1450,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="5"/>
-      <c r="B49" s="4"/>
+      <c r="A49" s="4"/>
+      <c r="B49" s="5"/>
       <c r="C49" t="s">
         <v>47</v>
       </c>
@@ -1466,8 +1466,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="5"/>
-      <c r="B50" s="4"/>
+      <c r="A50" s="4"/>
+      <c r="B50" s="5"/>
       <c r="C50" t="s">
         <v>48</v>
       </c>
@@ -1475,51 +1475,51 @@
         <v>118</v>
       </c>
       <c r="E50" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="5"/>
-      <c r="B51" s="4"/>
+      <c r="A51" s="4"/>
+      <c r="B51" s="5"/>
       <c r="C51" t="s">
         <v>49</v>
       </c>
       <c r="D51" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E51" t="s">
         <v>120</v>
       </c>
-      <c r="E51" t="s">
-        <v>121</v>
-      </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="5"/>
-      <c r="B52" s="4"/>
+      <c r="A52" s="4"/>
+      <c r="B52" s="5"/>
       <c r="C52" t="s">
         <v>102</v>
       </c>
       <c r="D52" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="E52" t="s">
         <v>122</v>
       </c>
-      <c r="E52" t="s">
-        <v>123</v>
-      </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="5"/>
-      <c r="B53" s="4"/>
+      <c r="A53" s="4"/>
+      <c r="B53" s="5"/>
       <c r="C53" t="s">
         <v>50</v>
       </c>
       <c r="D53" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E53" t="s">
         <v>124</v>
       </c>
-      <c r="E53" t="s">
-        <v>125</v>
-      </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="5"/>
-      <c r="B54" s="4"/>
+      <c r="A54" s="4"/>
+      <c r="B54" s="5"/>
       <c r="C54" t="s">
         <v>51</v>
       </c>
@@ -1534,8 +1534,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="5"/>
-      <c r="B55" s="4"/>
+      <c r="A55" s="4"/>
+      <c r="B55" s="5"/>
       <c r="C55" t="s">
         <v>52</v>
       </c>
@@ -1550,26 +1550,26 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="5"/>
-      <c r="B56" s="4"/>
+      <c r="A56" s="4"/>
+      <c r="B56" s="5"/>
       <c r="C56" t="s">
         <v>53</v>
       </c>
       <c r="D56" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E56" t="s">
         <v>126</v>
       </c>
-      <c r="E56" t="s">
-        <v>127</v>
-      </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="5"/>
-      <c r="B57" s="4"/>
+      <c r="A57" s="4"/>
+      <c r="B57" s="5"/>
       <c r="C57" t="s">
         <v>54</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E57" t="s">
         <v>117</v>
@@ -1578,6 +1578,15 @@
   </sheetData>
   <autoFilter ref="A1:T57" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="18">
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="B46:B57"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B15:B22"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="B30:B35"/>
     <mergeCell ref="A37:A41"/>
     <mergeCell ref="A43:A45"/>
     <mergeCell ref="A46:A57"/>
@@ -1587,18 +1596,12 @@
     <mergeCell ref="A15:A22"/>
     <mergeCell ref="A24:A28"/>
     <mergeCell ref="A30:A35"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="B46:B57"/>
-    <mergeCell ref="B3:B6"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B15:B22"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="B30:B35"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E50" r:id="rId1" xr:uid="{C4C61B05-9594-422A-9C30-A38799214227}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>